--- a/LC76_Phase2_WorkingPapers.xlsx
+++ b/LC76_Phase2_WorkingPapers.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="46" customWidth="1" style="20" min="1" max="1"/>
@@ -958,6 +958,18 @@
       <c r="B41" s="28" t="inlineStr">
         <is>
           <t>R1/R2 audit-clean (no edits). R31: boost 0.5→0.6 bar ×4, recon-derived →86,006 ×3, intercooler →~260,000 ×3; owner upgrade decisions (exhaust→Done; boost-gauge/alternator/ARP/airbox→Not Required). R11: odo→310,412; payload provisional (TA-002). R28: odo→310,412; payload '~551'; '(Andrea)' removed; 583 bar-primary. TA-032 &amp; TA-033 CLOSED. TA-002 (weighbridge) remains the sole open TA. Follow-on: boost-figure library sweep initiated (R11 done; R1/R13/R19/R23/R24/R27 candidates) + incidental stale-figure findings logged (Concordance r32) pending owner decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>PASS A/B — §5 STEP 1 DONE (R1 + R13 + R34)</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="inlineStr">
+        <is>
+          <t>22 Jun 2026: boost-add R1 + R13 (-&gt; 0.6 bar, bar-only); odo R34 masthead (-&gt; 310,412). TA-034 (boost-add) + TA-035 (odo/derived) FORMALISED — both Open (multi-session passes; close on full-sweep completion). Remaining boost-adds: R19/R23/R24/R27. Remaining odo/derived: R19/R20/R23/R27. Owner ruling 22 Jun: always bump edited-doc masthead date to session date. index.html 22 Jun (no-op); sw.js no bump. Open TAs now: TA-002, TA-034, TA-035.</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -4443,6 +4455,33 @@
       <c r="E33" s="20" t="inlineStr">
         <is>
           <t>R18 discrepancy resolved; install-km harmonised to 38,429</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Boost-add + odo/derived sweep — §5 step 1 (R1 + R13 + R34)</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Boost 0.6 bar (bar-only); current-odo 310,412 km</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>In progress — opened 22 Jun 2026 (TA-034 boost-add, TA-035 odo/derived); both Open</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>R1 (29.8KB): row-val -&gt; '0.6 bar · 118 kW / 373 Nm' (&amp;#183; entity). R13 (58.8KB): drivetrain line -&gt; '...with SAC turbo at 0.6 bar'; masthead Last Updated 24 Mar-&gt;22 Jun 2026. R34 (36.8KB): masthead ~310,000-&gt;310,412 km (sole occurrence; tilde dropped, middots untouched); no last-updated field (footer 'Compiled June 2026' = provenance, preserved). R1 has NO date element (nothing to bump). NEW STANDING RULE (owner, 22 Jun): always bump a doc's own masthead 'Last updated' to session date when worked on. Validation: div R1 190/190, R13 104/104, R34 84/84; JS OK; no stale ~310,000 / 0.5 bar in scope; events/costs preserved. index.html already 22 Jun (no-op); sw.js no bump.</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>TA-034 + TA-035 Open (session 1 of multi-file passes)</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="20" min="1" max="1"/>
@@ -6643,6 +6682,130 @@
       <c r="L35" s="42" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>TA-034</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>R1/R13/R19/R23/R24/R27</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>R1,R13,R19,R23,R24,R27</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>Spec / overview / masthead turbo refs</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>Turbo shown in spec/overview/masthead with no boost figure — add 0.6 bar (bar-only) for library consistency</t>
+        </is>
+      </c>
+      <c r="F36" s="41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>Consistency (no stale 0.5 bar exists anywhere)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>Udel Jun 2026 boost confirmation (0.6 bar)</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="41" t="inlineStr">
+        <is>
+          <t>Boost-add sweep — add 0.6 bar (bar-only)</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Remaining ADDs: R19/R23/R24/R27 (each its own session, &gt;80KB). Closes when full sweep done.</t>
+        </is>
+      </c>
+      <c r="L36" s="42" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>TA-035</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>R19/R20/R23/R27/R34</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>R19,R20,R23,R27,R34</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>Mastheads (current-odo) + derived turbo-km</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Stale current-odo mastheads ~310,000 -&gt; 310,412 km; stale derived turbo-km ~80,600 -&gt; ~86,006 km</t>
+        </is>
+      </c>
+      <c r="F37" s="41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>Current-vs-event-vs-cost discipline</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>Odometer read 19 Jun 2026 (310,412); recon base 224,406</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="41" t="inlineStr">
+        <is>
+          <t>Odo / derived-km propagation</t>
+        </is>
+      </c>
+      <c r="K37" s="20" t="inlineStr">
+        <is>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Remaining: R19/R27 mastheads (fold w/ boost), R20 masthead + derived ~80,600-&gt;~86,006, R23 derived ~80,600-&gt;~86,006. Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. Closes when full sweep done.</t>
+        </is>
+      </c>
+      <c r="L37" s="42" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>

--- a/LC76_Phase2_WorkingPapers.xlsx
+++ b/LC76_Phase2_WorkingPapers.xlsx
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -4482,6 +4482,33 @@
       <c r="E34" s="20" t="inlineStr">
         <is>
           <t>TA-034 + TA-035 Open (session 1 of multi-file passes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>§5 step 2 (R19 AT Tyre Review) — boost-add + odo, single session</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Boost 0.6 bar (bar-only); current odometer 310,412 km</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Applied 22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>R19 (96.7 KB, own session per &gt;80KB rule): two surgical edits in one fetch. Vehicle overview (l.316): 'SAC low-boost turbo · GVM 2,850 kg · ~310,000 km' -&gt; 'SAC low-boost turbo (0.6 bar) · GVM 2,850 kg · 310,412 km' (boost-add bar-only + current-odo refresh, tilde dropped). Masthead (l.296): Last Updated 06 Jun -&gt; 22 Jun 2026 (standing rule). Line 324 'low-boost turbo' prose left (not spec/overview/masthead). div 674/674 held, 1 script JS OK, stale sweep clean (no surviving ~310,000 / no 0.5-0.75 bar), events/install-km(38,429)/costs untouched. index.html already 22 Jun (no-op); sw.js no bump. TA-034 + TA-035 R19 portions done, both remain Open.</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>TA-034/TA-035 R19 done; both Open (R23/R24/R27 + R20/R23/R27 pending)</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6765,7 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Remaining ADDs: R19/R23/R24/R27 (each its own session, &gt;80KB). Closes when full sweep done.</t>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview turbo ref -&gt; '...SAC low-boost turbo (0.6 bar)...' (bar-only, folded w/ odo). Remaining ADDs: R23/R24/R27 (each its own session, &gt;80KB). Closes when full sweep done.</t>
         </is>
       </c>
       <c r="L36" s="42" t="inlineStr">
@@ -6800,7 +6827,7 @@
       </c>
       <c r="K37" s="20" t="inlineStr">
         <is>
-          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Remaining: R19/R27 mastheads (fold w/ boost), R20 masthead + derived ~80,600-&gt;~86,006, R23 derived ~80,600-&gt;~86,006. Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. Closes when full sweep done.</t>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview ~310,000-&gt;310,412 (sole current-odo occurrence; tilde dropped; folded w/ boost-add). Remaining: R27 (fold w/ boost), R20 masthead + derived ~80,600-&gt;~86,006, R23 derived ~80,600-&gt;~86,006. Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. Closes when full sweep done.</t>
         </is>
       </c>
       <c r="L37" s="42" t="inlineStr">

--- a/LC76_Phase2_WorkingPapers.xlsx
+++ b/LC76_Phase2_WorkingPapers.xlsx
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -4509,6 +4509,33 @@
       <c r="E35" s="20" t="inlineStr">
         <is>
           <t>TA-034/TA-035 R19 done; both Open (R23/R24/R27 + R20/R23/R27 pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>§5 step 3 (R23 Pre-Trip Prep Protocol) — boost-add + derived-km, single session</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Boost 0.6 bar (bar-only); derived turbo-km ~86,006 km</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>Applied 22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>R23 (90.6 KB, own session per &gt;80KB rule): three surgical edits in one fetch, all owner-approved. Masthead std-vehicle bar (l.448): 'SAC Low-Boost Turbo · R151F 5-Speed · GVM 2,850 kg · April 2026' -&gt; 'SAC Low-Boost Turbo (0.6 bar) · R151F 5-Speed · GVM 2,850 kg · June 2026' (boost-add bar-only + masthead month-year date bump Apr-&gt;Jun, standing rule; harmonises w/ footer). Footer spec bar (l.1595): 'SAC Low-Boost Turbo · ~310,412 km · June 2026' -&gt; 'SAC Low-Boost Turbo (0.6 bar) · ~310,412 km · June 2026' (boost-add bar-only, owner-approved 22 Jun). Derived turbo-km (l.1324): reconned Aug 2023 224,406 km '(~80,600 km ago)' -&gt; '(~86,006 km ago)' (lone straggler brought into line w/ ~86,006 already at 891/892; event 224,406 preserved). Current odo 310,412 already present (768/769/891/892/1595) - no odo edit. Coolant-cap 0.88 bar/13 psi (l.913) untouched (not boost). div 235/235 held, 2 scripts JS OK, stale sweep clean (no surviving ~80,600 / no 0.5-0.75 bar; ~86,006 x3, 224,406 x1), events/install-km(38,429)/costs untouched. index.html already 22 Jun (no-op); sw.js no bump. NOTE: R19 step-2 confirmed committed at tip (earlier main-raw mismatch was CDN propagation lag; SHA-pinned fetch verified). TA-034 + TA-035 R23 portions done, both remain Open.</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>TA-034/TA-035 R23 done; both Open (R24/R27 + R20/R27 pending)</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6792,7 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview turbo ref -&gt; '...SAC low-boost turbo (0.6 bar)...' (bar-only, folded w/ odo). Remaining ADDs: R23/R24/R27 (each its own session, &gt;80KB). Closes when full sweep done.</t>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview turbo ref -&gt; '...SAC low-boost turbo (0.6 bar)...' (bar-only, folded w/ odo). Session 3, 22 Jun 2026 (§5 step 3): R23 masthead + footer turbo refs -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; masthead folded w/ date Apr-&gt;Jun 2026, footer owner-approved). Remaining ADDs: R24/R27 (each its own session, &gt;80KB). Closes when full sweep done.</t>
         </is>
       </c>
       <c r="L36" s="42" t="inlineStr">
@@ -6827,7 +6854,7 @@
       </c>
       <c r="K37" s="20" t="inlineStr">
         <is>
-          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview ~310,000-&gt;310,412 (sole current-odo occurrence; tilde dropped; folded w/ boost-add). Remaining: R27 (fold w/ boost), R20 masthead + derived ~80,600-&gt;~86,006, R23 derived ~80,600-&gt;~86,006. Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. Closes when full sweep done.</t>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview ~310,000-&gt;310,412 (sole current-odo occurrence; tilde dropped; folded w/ boost-add). Session 3, 22 Jun 2026 (§5 step 3): R23 derived turbo-km ~80,600-&gt;~86,006 (l.1324; lone straggler brought into line w/ ~86,006 at 891/892; event 224,406 preserved; R23 odo 310,412 already current, no odo edit). Remaining: R27 (fold w/ boost), R20 masthead + derived ~80,600-&gt;~86,006. Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. Closes when full sweep done.</t>
         </is>
       </c>
       <c r="L37" s="42" t="inlineStr">

--- a/LC76_Phase2_WorkingPapers.xlsx
+++ b/LC76_Phase2_WorkingPapers.xlsx
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -4536,6 +4536,33 @@
       <c r="E36" s="20" t="inlineStr">
         <is>
           <t>TA-034/TA-035 R23 done; both Open (R24/R27 + R20/R27 pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>R23 triage table — valve-clearance verdict correction (owner-spotted)</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Valve clearances set Jun 2026 @ 310,412 km — IN INTERVAL</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>Applied 22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>R23 Triage Decision Table (l.585): valve-clearances Verdict 'CHECK &amp; SET' (verdict-replace, action-required styling) -&gt; 'IN INTERVAL' (verdict-leave). Stale verdict predating the Jun 2026 adjustment — clearances were set by Udel @ 310,412 km (12 shims, first recorded adjustment), 0 km ago. Now consistent with (a) its own Action cell 'Completed Jun 2026 — re-check ~40,000 km' and (b) the parallel Fuel-injectors row (same Jun 2026 / 310,412 km / freshly done, already IN INTERVAL). Action cell unchanged (already correct). div 235/235 held, 2 scripts JS OK, boost edits (l.448/1324/1595) preserved. Owner-spotted, out-of-original-R23-brief; executed under owner direction 22 Jun. Logged as Concordance note (not raised as TA) — internal-consistency fix, no external source. index.html 22 Jun (no-op); sw.js no bump.</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Triage verdict stale-state corrected; consistent w/ injectors row</t>
         </is>
       </c>
     </row>

--- a/LC76_Phase2_WorkingPapers.xlsx
+++ b/LC76_Phase2_WorkingPapers.xlsx
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -4563,6 +4563,33 @@
       <c r="E37" s="20" t="inlineStr">
         <is>
           <t>Triage verdict stale-state corrected; consistent w/ injectors row</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>§5 step 4 (R24 Fuel System &amp; Diesel Quality Guide) — boost-add only, single session</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Boost 0.6 bar (bar-only)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Applied 22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>R24 (96.4 KB, own session per &gt;80KB rule): single owner-chartered surgical edit in one fetch (SHA-pinned; main-raw matched, no CDN lag today). Masthead mh-vehicle bar (l.373): 'SAC Low-Boost Turbo · 145L Main' -&gt; 'SAC Low-Boost Turbo (0.6 bar) · 145L Main' (boost-add bar-only). 'SAC Low-Boost Turbo' appears exactly ONCE in the file — this masthead bar is the only turbo reference; no spec/overview/footer turbo line to harmonise. R24 carries NO date element anywhere (no masthead date / 'Last Updated' / 'Compiled' / footer date) -&gt; standing date-bump rule is a no-op (same as R1); no date field invented. Pure ADD, not a correction: pre-edit sweep 0.6/0.5/0.75 bar all = 0. No odo/derived/event figures in file (310,412 / ~310,000 / 80,600 / 86,006 / 224,406 / 38,429 all = 0) — none introduced. div 484/484 held, 1 script JS OK, size +10 B (ASCII ' (0.6 bar)'). index.html already 22 Jun (no-op); sw.js no bump (existing-file edit). TA-034 R24 portion done; R24 out of TA-035 scope (no odo/derived). TA-034 remains Open (R27 last).</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>TA-034 R24 done; Open (R27 pending). TA-035 N/A to R24 (no odo/derived)</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6846,7 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview turbo ref -&gt; '...SAC low-boost turbo (0.6 bar)...' (bar-only, folded w/ odo). Session 3, 22 Jun 2026 (§5 step 3): R23 masthead + footer turbo refs -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; masthead folded w/ date Apr-&gt;Jun 2026, footer owner-approved). Remaining ADDs: R24/R27 (each its own session, &gt;80KB). Closes when full sweep done.</t>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview turbo ref -&gt; '...SAC low-boost turbo (0.6 bar)...' (bar-only, folded w/ odo). Session 3, 22 Jun 2026 (§5 step 3): R23 masthead + footer turbo refs -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; masthead folded w/ date Apr-&gt;Jun 2026, footer owner-approved). Session 4, 22 Jun 2026 (§5 step 4): R24 masthead mh-vehicle bar (l.373) -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; sole turbo ref in file, single occurrence; R24 has no date element so no date bump; no odo/derived/event figures present). Remaining ADDs: R27 (own session, &gt;80KB). Closes when full sweep done.</t>
         </is>
       </c>
       <c r="L36" s="42" t="inlineStr">

--- a/LC76_Phase2_WorkingPapers.xlsx
+++ b/LC76_Phase2_WorkingPapers.xlsx
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -4590,6 +4590,33 @@
       <c r="E38" s="20" t="inlineStr">
         <is>
           <t>TA-034 R24 done; Open (R27 pending). TA-035 N/A to R24 (no odo/derived)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>§5 step 5 (R27 Bush Mechanics Field Guide) — combined masthead boost-add + odo</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Boost 0.6 bar (bar-only); current-odo 310,412 km</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>Applied 23 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>R27 (127.0 KB, own session per &gt;80KB rule): single combined masthead str_replace (l.339 mh-vehicle) — boost-add (0.6 bar, bar-only) + odo ~310,000-&gt;310,412 (exact, tilde dropped). div 815/815; 1 script JS OK. Contextual L828/L830 ~310,000 left per policy. Events 202,066 / 310,412 (valve-set) / 275,000 preserved. No date element so no date bump. No derived turbo-km in file.</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>TA-034 R27 done — boost-add sweep COMPLETE (R1/R13/R19/R23/R24/R27); TA-034 CLOSED. TA-035 R27 masthead odo done; stays Open (R20 pending).</t>
         </is>
       </c>
     </row>
@@ -6846,12 +6873,12 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview turbo ref -&gt; '...SAC low-boost turbo (0.6 bar)...' (bar-only, folded w/ odo). Session 3, 22 Jun 2026 (§5 step 3): R23 masthead + footer turbo refs -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; masthead folded w/ date Apr-&gt;Jun 2026, footer owner-approved). Session 4, 22 Jun 2026 (§5 step 4): R24 masthead mh-vehicle bar (l.373) -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; sole turbo ref in file, single occurrence; R24 has no date element so no date bump; no odo/derived/event figures present). Remaining ADDs: R27 (own session, &gt;80KB). Closes when full sweep done.</t>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R1 row-val -&gt; '0.6 bar · 118 kW / 373 Nm'; R13 drivetrain line -&gt; '...with SAC turbo at 0.6 bar'. R8/R21 already 0.6 bar (reference, untouched). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview turbo ref -&gt; '...SAC low-boost turbo (0.6 bar)...' (bar-only, folded w/ odo). Session 3, 22 Jun 2026 (§5 step 3): R23 masthead + footer turbo refs -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; masthead folded w/ date Apr-&gt;Jun 2026, footer owner-approved). Session 4, 22 Jun 2026 (§5 step 4): R24 masthead mh-vehicle bar (l.373) -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; sole turbo ref in file, single occurrence; R24 has no date element so no date bump; no odo/derived/event figures present). Session 5, 23 Jun 2026 (§5 step 5): R27 masthead mh-vehicle bar (l.339) -&gt; '...SAC Low-Boost Turbo (0.6 bar)...' (bar-only; sole turbo ref in file, single occurrence; folded w/ odo; no date element so no date bump). Sweep COMPLETE — all boost-adds applied (R1/R13/R19/R23/R24/R27).</t>
         </is>
       </c>
       <c r="L36" s="42" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6935,7 @@
       </c>
       <c r="K37" s="20" t="inlineStr">
         <is>
-          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview ~310,000-&gt;310,412 (sole current-odo occurrence; tilde dropped; folded w/ boost-add). Session 3, 22 Jun 2026 (§5 step 3): R23 derived turbo-km ~80,600-&gt;~86,006 (l.1324; lone straggler brought into line w/ ~86,006 at 891/892; event 224,406 preserved; R23 odo 310,412 already current, no odo edit). Remaining: R27 (fold w/ boost), R20 masthead + derived ~80,600-&gt;~86,006. Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. Closes when full sweep done.</t>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview ~310,000-&gt;310,412 (sole current-odo occurrence; tilde dropped; folded w/ boost-add). Session 3, 22 Jun 2026 (§5 step 3): R23 derived turbo-km ~80,600-&gt;~86,006 (l.1324; lone straggler brought into line w/ ~86,006 at 891/892; event 224,406 preserved; R23 odo 310,412 already current, no odo edit). Session 5, 23 Jun 2026 (§5 step 5): R27 masthead ~310,000-&gt;310,412 (exact; tilde dropped; folded w/ boost-add). Contextual L828/L830 left per policy. Remaining: R20 masthead + derived ~80,600-&gt;~86,006. Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. Closes when full sweep done.</t>
         </is>
       </c>
       <c r="L37" s="42" t="inlineStr">

--- a/LC76_Phase2_WorkingPapers.xlsx
+++ b/LC76_Phase2_WorkingPapers.xlsx
@@ -3609,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -4617,6 +4617,33 @@
       <c r="E39" s="20" t="inlineStr">
         <is>
           <t>TA-034 R27 done — boost-add sweep COMPLETE (R1/R13/R19/R23/R24/R27); TA-034 CLOSED. TA-035 R27 masthead odo done; stays Open (R20 pending).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>§5 step 6 (R20 Seal &amp; Gasket Atlas) — masthead odo + date + derived turbo-km, single session</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>current-odo 310,412 km; derived turbo-km ~86,006 km</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>Applied 23 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>R20 (131.5 KB, own session per &gt;80KB rule): three text-only surgical edits in one SHA-pinned fetch (main-raw matched, no CDN lag). Edit 1 masthead l.317 (ms-vehicle): odo ~310,000-&gt;310,412 (exact, tilde dropped) folded with masthead date 04 June-&gt;23 June 2026. Edit 2 derived turbo-km l.943: ~80,600-&gt;~86,006 (tilde kept, delta 310,412-224,406); recon event 224,406 preserved in same sentence. Edit 3 footer l.2045: Updated April-&gt;June 2026 per owner D1 (masthead/footer date-element alignment). div 1304/1304; 1 script JS OK; size 134,650-&gt;134,648 B (-2). Contextual l.348/l.367 ~310,000 left per TA-035 policy. No boost in file (0.6 bar = 0; none added — R20 outside boost sweep). index.html date already current; sw.js no bump (existing-file edit).</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>TA-035 CLOSED — odo/derived sweep complete (R20 was the last odo/derived file). Open now = 1 (TA-002 weighbridge, owner-gated).</t>
         </is>
       </c>
     </row>
@@ -6935,12 +6962,12 @@
       </c>
       <c r="K37" s="20" t="inlineStr">
         <is>
-          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview ~310,000-&gt;310,412 (sole current-odo occurrence; tilde dropped; folded w/ boost-add). Session 3, 22 Jun 2026 (§5 step 3): R23 derived turbo-km ~80,600-&gt;~86,006 (l.1324; lone straggler brought into line w/ ~86,006 at 891/892; event 224,406 preserved; R23 odo 310,412 already current, no odo edit). Session 5, 23 Jun 2026 (§5 step 5): R27 masthead ~310,000-&gt;310,412 (exact; tilde dropped; folded w/ boost-add). Contextual L828/L830 left per policy. Remaining: R20 masthead + derived ~80,600-&gt;~86,006. Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. Closes when full sweep done.</t>
+          <t>Session 1, 22 Jun 2026 (§5 step 1): R34 masthead ~310,000-&gt;310,412 (sole occurrence in file; tilde dropped). Session 2, 22 Jun 2026 (§5 step 2): R19 vehicle-overview ~310,000-&gt;310,412 (sole current-odo occurrence; tilde dropped; folded w/ boost-add). Session 3, 22 Jun 2026 (§5 step 3): R23 derived turbo-km ~80,600-&gt;~86,006 (l.1324; lone straggler brought into line w/ ~86,006 at 891/892; event 224,406 preserved; R23 odo 310,412 already current, no odo edit). Session 5, 23 Jun 2026 (§5 step 5): R27 masthead ~310,000-&gt;310,412 (exact; tilde dropped; folded w/ boost-add). Contextual L828/L830 left per policy. Session 6, 23 Jun 2026 (§5 step 6): R20 masthead ~310,000-&gt;310,412 (exact, tilde dropped) + masthead date 04 Jun-&gt;23 Jun; derived turbo-km ~80,600-&gt;~86,006 (l.943, tilde kept, delta 310,412-224,406); footer date April-&gt;June per owner D1; contextual l.348/l.367 left per policy. Sweep COMPLETE — all odo/derived files done (R20 last). Contextual ~310,000 (R18 x5 / R25 / R20 x2 / R27 x2): default LEAVE. R8 310,000 = milestone labels PRESERVE. Events / install-km (38,429) / costs preserved. TA-035 CLOSED — odo/derived sweep complete.</t>
         </is>
       </c>
       <c r="L37" s="42" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
